--- a/tibetan_associations/tibetan_variant_lookup.xlsx
+++ b/tibetan_associations/tibetan_variant_lookup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wgu/Desktop/CMSNetwork/tibetan_associations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056C2633-22E8-9D45-A6BB-DD9B0E65091B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5D60A6-4B58-6840-93BE-F2260F5333EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
